--- a/Employee_Reports_wi48/Dominic Munyua Kanyotu Q0437.xlsx
+++ b/Employee_Reports_wi48/Dominic Munyua Kanyotu Q0437.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-333</v>
+        <v>-336</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1342,11 +1342,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1379,11 +1379,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1416,11 +1416,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1465,11 +1465,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
